--- a/Biosci Reader_06.04.26.xlsx
+++ b/Biosci Reader_06.04.26.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45892ED-6763-45E9-9843-8CBFBE4C70F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E35092-E79F-486A-AA3C-50FE94C83D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="218" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="218" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="2" r:id="rId1"/>
@@ -2969,23 +2969,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K260"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="45.44140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="45.42578125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" style="2" customWidth="1"/>
     <col min="8" max="8" width="20" style="2" customWidth="1"/>
-    <col min="9" max="9" width="42.77734375" style="34" customWidth="1"/>
-    <col min="10" max="10" width="37.21875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.21875" style="5"/>
-    <col min="12" max="16384" width="9.21875" style="1"/>
+    <col min="9" max="9" width="42.7109375" style="34" customWidth="1"/>
+    <col min="10" max="10" width="37.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.28515625" style="5"/>
+    <col min="12" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="107" t="s">
         <v>545</v>
       </c>
@@ -2998,7 +2998,7 @@
       <c r="H1" s="92"/>
       <c r="I1" s="38"/>
     </row>
-    <row r="2" spans="1:11" s="3" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="3" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -3046,7 +3046,7 @@
       <c r="J3" s="96"/>
       <c r="K3" s="12"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="4"/>
       <c r="C4" s="6"/>
@@ -3058,7 +3058,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="97"/>
     </row>
-    <row r="5" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>9</v>
       </c>
@@ -3073,7 +3073,7 @@
       <c r="J5" s="96"/>
       <c r="K5" s="12"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="9"/>
@@ -3085,7 +3085,7 @@
       <c r="I6" s="33"/>
       <c r="J6" s="97"/>
     </row>
-    <row r="7" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>10</v>
       </c>
@@ -3100,7 +3100,7 @@
       <c r="J7" s="96"/>
       <c r="K7" s="12"/>
     </row>
-    <row r="8" spans="1:11" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="45.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>1</v>
       </c>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="J8" s="97"/>
     </row>
-    <row r="9" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2</v>
       </c>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="J9" s="97"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>3</v>
       </c>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="J10" s="97"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>4</v>
       </c>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="J11" s="97"/>
     </row>
-    <row r="12" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>5</v>
       </c>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="J12" s="97"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>6</v>
       </c>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="J13" s="97"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>7</v>
       </c>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="J14" s="97"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -3286,7 +3286,7 @@
       <c r="I15" s="33"/>
       <c r="J15" s="97"/>
     </row>
-    <row r="16" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>15</v>
       </c>
@@ -3301,7 +3301,7 @@
       <c r="J16" s="96"/>
       <c r="K16" s="12"/>
     </row>
-    <row r="17" spans="1:11" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="15"/>
       <c r="C17" s="71" t="s">
@@ -3320,7 +3320,7 @@
       <c r="J17" s="96"/>
       <c r="K17" s="12"/>
     </row>
-    <row r="18" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="68" t="s">
         <v>486</v>
@@ -3345,7 +3345,7 @@
       <c r="J18" s="96"/>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="68" t="s">
         <v>487</v>
@@ -3370,7 +3370,7 @@
       <c r="J19" s="96"/>
       <c r="K19" s="12"/>
     </row>
-    <row r="20" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="68" t="s">
         <v>488</v>
@@ -3395,7 +3395,7 @@
       <c r="J20" s="96"/>
       <c r="K20" s="12"/>
     </row>
-    <row r="21" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="68" t="s">
         <v>102</v>
@@ -3426,7 +3426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -3439,7 +3439,7 @@
       <c r="J22" s="96"/>
       <c r="K22" s="12"/>
     </row>
-    <row r="23" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15"/>
       <c r="B23" s="74" t="s">
         <v>209</v>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="K23" s="15"/>
     </row>
-    <row r="24" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15"/>
       <c r="B24" s="15" t="s">
         <v>212</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="K24" s="15"/>
     </row>
-    <row r="25" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
       <c r="B25" s="15" t="s">
         <v>216</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="K25" s="15"/>
     </row>
-    <row r="26" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15"/>
       <c r="B26" s="15" t="s">
         <v>219</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="K26" s="15"/>
     </row>
-    <row r="27" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15"/>
       <c r="B27" s="15" t="s">
         <v>222</v>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="K27" s="15"/>
     </row>
-    <row r="28" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="18"/>
       <c r="B28" s="24"/>
       <c r="C28" s="18"/>
@@ -3584,7 +3584,7 @@
       <c r="J28" s="96"/>
       <c r="K28" s="12"/>
     </row>
-    <row r="29" spans="1:11" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="18"/>
       <c r="B29" s="15"/>
       <c r="C29" s="71" t="s">
@@ -3603,7 +3603,7 @@
       <c r="J29" s="96"/>
       <c r="K29" s="12"/>
     </row>
-    <row r="30" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="18"/>
       <c r="B30" s="15" t="s">
         <v>489</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="K30" s="12"/>
     </row>
-    <row r="31" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="18"/>
       <c r="B31" s="15" t="s">
         <v>490</v>
@@ -3667,7 +3667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="18"/>
       <c r="B32" s="15" t="s">
         <v>491</v>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K32" s="12"/>
     </row>
-    <row r="33" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15"/>
       <c r="B33" s="15" t="s">
         <v>103</v>
@@ -3727,7 +3727,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="18"/>
       <c r="B34" s="24"/>
       <c r="C34" s="18"/>
@@ -3740,7 +3740,7 @@
       <c r="J34" s="96"/>
       <c r="K34" s="12"/>
     </row>
-    <row r="35" spans="1:11" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="18"/>
       <c r="B35" s="15"/>
       <c r="C35" s="71" t="s">
@@ -3759,7 +3759,7 @@
       <c r="J35" s="96"/>
       <c r="K35" s="12"/>
     </row>
-    <row r="36" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="18"/>
       <c r="B36" s="86" t="s">
         <v>492</v>
@@ -3792,7 +3792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="18"/>
       <c r="B37" s="86" t="s">
         <v>493</v>
@@ -3825,7 +3825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="18"/>
       <c r="B38" s="86" t="s">
         <v>494</v>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="K38" s="12"/>
     </row>
-    <row r="39" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="18"/>
       <c r="B39" s="86" t="s">
         <v>495</v>
@@ -3887,7 +3887,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="18"/>
       <c r="B40" s="24"/>
       <c r="C40" s="18"/>
@@ -3900,7 +3900,7 @@
       <c r="J40" s="96"/>
       <c r="K40" s="12"/>
     </row>
-    <row r="41" spans="1:11" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="18"/>
       <c r="B41" s="15"/>
       <c r="C41" s="71" t="s">
@@ -3919,7 +3919,7 @@
       <c r="J41" s="96"/>
       <c r="K41" s="12"/>
     </row>
-    <row r="42" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="18"/>
       <c r="B42" s="86" t="s">
         <v>496</v>
@@ -3952,7 +3952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="18"/>
       <c r="B43" s="86" t="s">
         <v>497</v>
@@ -3985,7 +3985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="18"/>
       <c r="B44" s="86" t="s">
         <v>498</v>
@@ -4018,7 +4018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="18"/>
       <c r="B45" s="86" t="s">
         <v>499</v>
@@ -4051,7 +4051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="18"/>
       <c r="B46" s="86" t="s">
         <v>500</v>
@@ -4080,7 +4080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="18"/>
       <c r="B47" s="86" t="s">
         <v>501</v>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="K47" s="12"/>
     </row>
-    <row r="48" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="18"/>
       <c r="B48" s="15" t="s">
         <v>502</v>
@@ -4140,7 +4140,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="18"/>
       <c r="B49" s="24"/>
       <c r="C49" s="15"/>
@@ -4153,7 +4153,7 @@
       <c r="J49" s="96"/>
       <c r="K49" s="12"/>
     </row>
-    <row r="50" spans="1:11" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="18"/>
       <c r="B50" s="15"/>
       <c r="C50" s="71" t="s">
@@ -4172,7 +4172,7 @@
       <c r="J50" s="96"/>
       <c r="K50" s="12"/>
     </row>
-    <row r="51" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="18"/>
       <c r="B51" s="86" t="s">
         <v>505</v>
@@ -4205,7 +4205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="18"/>
       <c r="B52" s="86" t="s">
         <v>506</v>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="K52" s="12"/>
     </row>
-    <row r="53" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="18"/>
       <c r="B53" s="86" t="s">
         <v>507</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="K53" s="12"/>
     </row>
-    <row r="54" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="18"/>
       <c r="B54" s="86" t="s">
         <v>508</v>
@@ -4300,7 +4300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="18"/>
       <c r="B55" s="86" t="s">
         <v>509</v>
@@ -4333,7 +4333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="18"/>
       <c r="B56" s="15"/>
       <c r="C56" s="18"/>
@@ -4346,7 +4346,7 @@
       <c r="J56" s="96"/>
       <c r="K56" s="12"/>
     </row>
-    <row r="57" spans="1:11" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="18"/>
       <c r="B57" s="15"/>
       <c r="C57" s="71" t="s">
@@ -4363,7 +4363,7 @@
       <c r="J57" s="96"/>
       <c r="K57" s="12"/>
     </row>
-    <row r="58" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="18"/>
       <c r="B58" s="68" t="s">
         <v>104</v>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="K58" s="12"/>
     </row>
-    <row r="59" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
       <c r="B59" s="68" t="s">
         <v>105</v>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="K59" s="12"/>
     </row>
-    <row r="60" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="15"/>
       <c r="B60" s="68" t="s">
         <v>106</v>
@@ -4454,7 +4454,7 @@
       <c r="J60" s="99"/>
       <c r="K60" s="15"/>
     </row>
-    <row r="61" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="15"/>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -4467,7 +4467,7 @@
       <c r="J61" s="99"/>
       <c r="K61" s="15"/>
     </row>
-    <row r="62" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="15"/>
       <c r="B62" s="15"/>
       <c r="C62" s="71" t="s">
@@ -4484,7 +4484,7 @@
       <c r="J62" s="99"/>
       <c r="K62" s="15"/>
     </row>
-    <row r="63" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="15"/>
       <c r="B63" s="68" t="s">
         <v>510</v>
@@ -4517,7 +4517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="15"/>
       <c r="B64" s="68" t="s">
         <v>511</v>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="K64" s="15"/>
     </row>
-    <row r="65" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="15"/>
       <c r="B65" s="68" t="s">
         <v>512</v>
@@ -4581,7 +4581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="15"/>
       <c r="B66" s="68" t="s">
         <v>513</v>
@@ -4614,7 +4614,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="15"/>
       <c r="B67" s="68" t="s">
         <v>514</v>
@@ -4647,7 +4647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="15"/>
       <c r="B68" s="68" t="s">
         <v>515</v>
@@ -4680,7 +4680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="15"/>
       <c r="B69" s="68" t="s">
         <v>516</v>
@@ -4713,7 +4713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="15"/>
       <c r="B70" s="68" t="s">
         <v>517</v>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="K70" s="15"/>
     </row>
-    <row r="71" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="15"/>
       <c r="B71" s="68" t="s">
         <v>518</v>
@@ -4777,7 +4777,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="15"/>
       <c r="B72" s="68" t="s">
         <v>519</v>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="K72" s="15"/>
     </row>
-    <row r="73" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="15"/>
       <c r="B73" s="68" t="s">
         <v>482</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K73" s="15"/>
     </row>
-    <row r="74" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="15"/>
       <c r="B74" s="68"/>
       <c r="C74" s="68"/>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="K74" s="15"/>
     </row>
-    <row r="75" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="15"/>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -4873,7 +4873,7 @@
       <c r="J75" s="99"/>
       <c r="K75" s="15"/>
     </row>
-    <row r="76" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="15"/>
       <c r="B76" s="15"/>
       <c r="C76" s="71" t="s">
@@ -4890,7 +4890,7 @@
       <c r="J76" s="99"/>
       <c r="K76" s="15"/>
     </row>
-    <row r="77" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="15"/>
       <c r="B77" s="68" t="s">
         <v>520</v>
@@ -4923,7 +4923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="15"/>
       <c r="B78" s="68" t="s">
         <v>521</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="K78" s="15"/>
     </row>
-    <row r="79" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="15"/>
       <c r="B79" s="68" t="s">
         <v>522</v>
@@ -4987,7 +4987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="15"/>
       <c r="B80" s="68" t="s">
         <v>523</v>
@@ -5020,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="15"/>
       <c r="B81" s="68" t="s">
         <v>552</v>
@@ -5053,7 +5053,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="15"/>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -5066,7 +5066,7 @@
       <c r="J82" s="99"/>
       <c r="K82" s="15"/>
     </row>
-    <row r="83" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="15"/>
       <c r="B83" s="15"/>
       <c r="C83" s="71" t="s">
@@ -5083,7 +5083,7 @@
       <c r="J83" s="99"/>
       <c r="K83" s="15"/>
     </row>
-    <row r="84" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="15"/>
       <c r="B84" s="68" t="s">
         <v>524</v>
@@ -5116,7 +5116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="15"/>
       <c r="B85" s="68" t="s">
         <v>525</v>
@@ -5149,7 +5149,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="15"/>
       <c r="B86" s="68" t="s">
         <v>526</v>
@@ -5182,7 +5182,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="87" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="15"/>
       <c r="B87" s="68" t="s">
         <v>527</v>
@@ -5215,7 +5215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="15"/>
       <c r="B88" s="15"/>
       <c r="C88" s="68"/>
@@ -5228,7 +5228,7 @@
       <c r="J88" s="99"/>
       <c r="K88" s="15"/>
     </row>
-    <row r="89" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="15"/>
       <c r="B89" s="15"/>
       <c r="C89" s="71" t="s">
@@ -5245,7 +5245,7 @@
       <c r="J89" s="99"/>
       <c r="K89" s="15"/>
     </row>
-    <row r="90" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="15"/>
       <c r="B90" s="68" t="s">
         <v>528</v>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="K90" s="15"/>
     </row>
-    <row r="91" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="15"/>
       <c r="B91" s="68" t="s">
         <v>529</v>
@@ -5305,7 +5305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="15"/>
       <c r="B92" s="68" t="s">
         <v>530</v>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="K92" s="15"/>
     </row>
-    <row r="93" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="15"/>
       <c r="B93" s="68" t="s">
         <v>531</v>
@@ -5369,7 +5369,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="15"/>
       <c r="B94" s="68" t="s">
         <v>532</v>
@@ -5394,7 +5394,7 @@
       <c r="J94" s="99"/>
       <c r="K94" s="15"/>
     </row>
-    <row r="95" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="15"/>
       <c r="B95" s="68" t="s">
         <v>533</v>
@@ -5423,7 +5423,7 @@
       <c r="J95" s="99"/>
       <c r="K95" s="15"/>
     </row>
-    <row r="96" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="18"/>
       <c r="B96" s="24"/>
       <c r="C96" s="15"/>
@@ -5436,7 +5436,7 @@
       <c r="J96" s="96"/>
       <c r="K96" s="12"/>
     </row>
-    <row r="97" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="18" t="s">
         <v>23</v>
       </c>
@@ -5451,7 +5451,7 @@
       <c r="J97" s="99"/>
       <c r="K97" s="15"/>
     </row>
-    <row r="98" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="15">
         <v>1</v>
       </c>
@@ -5480,7 +5480,7 @@
       <c r="J98" s="99"/>
       <c r="K98" s="15"/>
     </row>
-    <row r="99" spans="1:11" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="15">
         <v>2</v>
       </c>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K99" s="15"/>
     </row>
-    <row r="100" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>3</v>
       </c>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="J100" s="97"/>
     </row>
-    <row r="101" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="15">
         <v>4</v>
       </c>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="J101" s="97"/>
     </row>
-    <row r="102" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="15">
         <v>5</v>
       </c>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="J102" s="97"/>
     </row>
-    <row r="103" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>6</v>
       </c>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="J103" s="97"/>
     </row>
-    <row r="104" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="15">
         <v>7</v>
       </c>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="J104" s="97"/>
     </row>
-    <row r="105" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A105" s="15">
         <v>8</v>
       </c>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="J105" s="97"/>
     </row>
-    <row r="106" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>9</v>
       </c>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="J106" s="97"/>
     </row>
-    <row r="107" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="15">
         <v>10</v>
       </c>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="J107" s="97"/>
     </row>
-    <row r="108" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="15">
         <v>11</v>
       </c>
@@ -5743,7 +5743,7 @@
       <c r="I108" s="46"/>
       <c r="J108" s="97"/>
     </row>
-    <row r="109" spans="1:11" s="16" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" s="16" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>12</v>
       </c>
@@ -5770,7 +5770,7 @@
       <c r="J109" s="99"/>
       <c r="K109" s="15"/>
     </row>
-    <row r="110" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="15">
         <v>13</v>
       </c>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="J110" s="97"/>
     </row>
-    <row r="111" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="15">
         <v>14</v>
       </c>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="J111" s="97"/>
     </row>
-    <row r="112" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>15</v>
       </c>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="J112" s="97"/>
     </row>
-    <row r="113" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="15">
         <v>16</v>
       </c>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="J113" s="97"/>
     </row>
-    <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="15">
         <v>17</v>
       </c>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="J114" s="97"/>
     </row>
-    <row r="115" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>18</v>
       </c>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="J115" s="97"/>
     </row>
-    <row r="116" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -5938,7 +5938,7 @@
       <c r="I116" s="33"/>
       <c r="J116" s="97"/>
     </row>
-    <row r="117" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="18" t="s">
         <v>33</v>
       </c>
@@ -5952,7 +5952,7 @@
       <c r="J117" s="96"/>
       <c r="K117" s="12"/>
     </row>
-    <row r="118" spans="1:11" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5">
         <v>1</v>
       </c>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="J118" s="97"/>
     </row>
-    <row r="119" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5">
         <v>2</v>
       </c>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="J119" s="97"/>
     </row>
-    <row r="120" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5">
         <v>3</v>
       </c>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="J120" s="97"/>
     </row>
-    <row r="121" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="47">
         <v>4</v>
       </c>
@@ -6050,7 +6050,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5">
         <v>5</v>
       </c>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="J122" s="97"/>
     </row>
-    <row r="123" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>6</v>
       </c>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="J123" s="97"/>
     </row>
-    <row r="124" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5">
         <v>7</v>
       </c>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="J124" s="97"/>
     </row>
-    <row r="125" spans="1:11" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5">
         <v>8</v>
       </c>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="J125" s="97"/>
     </row>
-    <row r="126" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -6159,7 +6159,7 @@
       <c r="J126" s="99"/>
       <c r="K126" s="15"/>
     </row>
-    <row r="127" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A127" s="18" t="s">
         <v>35</v>
       </c>
@@ -6176,7 +6176,7 @@
       <c r="J127" s="99"/>
       <c r="K127" s="15"/>
     </row>
-    <row r="128" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A128" s="18"/>
       <c r="B128" s="76" t="s">
         <v>109</v>
@@ -6197,7 +6197,7 @@
       <c r="J128" s="99"/>
       <c r="K128" s="15"/>
     </row>
-    <row r="129" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A129" s="18"/>
       <c r="B129" s="76" t="s">
         <v>110</v>
@@ -6218,7 +6218,7 @@
       <c r="J129" s="99"/>
       <c r="K129" s="15"/>
     </row>
-    <row r="130" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A130" s="18"/>
       <c r="B130" s="76" t="s">
         <v>111</v>
@@ -6239,7 +6239,7 @@
       <c r="J130" s="99"/>
       <c r="K130" s="15"/>
     </row>
-    <row r="131" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A131" s="18"/>
       <c r="B131" s="76" t="s">
         <v>112</v>
@@ -6260,7 +6260,7 @@
       <c r="J131" s="99"/>
       <c r="K131" s="15"/>
     </row>
-    <row r="132" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A132" s="18"/>
       <c r="B132" s="76" t="s">
         <v>113</v>
@@ -6281,7 +6281,7 @@
       <c r="J132" s="99"/>
       <c r="K132" s="15"/>
     </row>
-    <row r="133" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A133" s="18"/>
       <c r="B133" s="76" t="s">
         <v>114</v>
@@ -6302,7 +6302,7 @@
       <c r="J133" s="99"/>
       <c r="K133" s="15"/>
     </row>
-    <row r="134" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A134" s="18"/>
       <c r="B134" s="76" t="s">
         <v>115</v>
@@ -6323,7 +6323,7 @@
       <c r="J134" s="99"/>
       <c r="K134" s="15"/>
     </row>
-    <row r="135" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A135" s="18"/>
       <c r="B135" s="76" t="s">
         <v>116</v>
@@ -6344,7 +6344,7 @@
       <c r="J135" s="99"/>
       <c r="K135" s="15"/>
     </row>
-    <row r="136" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A136" s="18"/>
       <c r="B136" s="76" t="s">
         <v>117</v>
@@ -6365,7 +6365,7 @@
       <c r="J136" s="99"/>
       <c r="K136" s="15"/>
     </row>
-    <row r="137" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A137" s="18"/>
       <c r="B137" s="76" t="s">
         <v>118</v>
@@ -6386,7 +6386,7 @@
       <c r="J137" s="99"/>
       <c r="K137" s="15"/>
     </row>
-    <row r="138" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A138" s="18"/>
       <c r="B138" s="76" t="s">
         <v>119</v>
@@ -6407,7 +6407,7 @@
       <c r="J138" s="99"/>
       <c r="K138" s="15"/>
     </row>
-    <row r="139" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A139" s="18"/>
       <c r="B139" s="76" t="s">
         <v>120</v>
@@ -6428,7 +6428,7 @@
       <c r="J139" s="99"/>
       <c r="K139" s="15"/>
     </row>
-    <row r="140" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A140" s="18"/>
       <c r="B140" s="76" t="s">
         <v>121</v>
@@ -6449,7 +6449,7 @@
       <c r="J140" s="99"/>
       <c r="K140" s="15"/>
     </row>
-    <row r="141" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A141" s="18"/>
       <c r="B141" s="84" t="s">
         <v>336</v>
@@ -6470,7 +6470,7 @@
       <c r="J141" s="99"/>
       <c r="K141" s="15"/>
     </row>
-    <row r="142" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A142" s="18"/>
       <c r="B142" s="76" t="s">
         <v>122</v>
@@ -6491,7 +6491,7 @@
       <c r="J142" s="99"/>
       <c r="K142" s="15"/>
     </row>
-    <row r="143" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A143" s="18"/>
       <c r="B143" s="76" t="s">
         <v>123</v>
@@ -6512,7 +6512,7 @@
       <c r="J143" s="99"/>
       <c r="K143" s="15"/>
     </row>
-    <row r="144" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A144" s="18"/>
       <c r="B144" s="76" t="s">
         <v>124</v>
@@ -6533,7 +6533,7 @@
       <c r="J144" s="99"/>
       <c r="K144" s="15"/>
     </row>
-    <row r="145" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A145" s="18"/>
       <c r="B145" s="76" t="s">
         <v>125</v>
@@ -6554,7 +6554,7 @@
       <c r="J145" s="99"/>
       <c r="K145" s="15"/>
     </row>
-    <row r="146" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A146" s="18"/>
       <c r="B146" s="76" t="s">
         <v>126</v>
@@ -6575,7 +6575,7 @@
       <c r="J146" s="99"/>
       <c r="K146" s="15"/>
     </row>
-    <row r="147" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A147" s="18"/>
       <c r="B147" s="76" t="s">
         <v>127</v>
@@ -6596,7 +6596,7 @@
       <c r="J147" s="99"/>
       <c r="K147" s="15"/>
     </row>
-    <row r="148" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A148" s="18"/>
       <c r="B148" s="76" t="s">
         <v>128</v>
@@ -6617,7 +6617,7 @@
       <c r="J148" s="99"/>
       <c r="K148" s="15"/>
     </row>
-    <row r="149" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A149" s="18"/>
       <c r="B149" s="76" t="s">
         <v>129</v>
@@ -6638,7 +6638,7 @@
       <c r="J149" s="99"/>
       <c r="K149" s="15"/>
     </row>
-    <row r="150" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A150" s="18"/>
       <c r="B150" s="76" t="s">
         <v>130</v>
@@ -6661,7 +6661,7 @@
       <c r="J150" s="99"/>
       <c r="K150" s="15"/>
     </row>
-    <row r="151" spans="1:11" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A151" s="18"/>
       <c r="B151" s="76" t="s">
         <v>205</v>
@@ -6682,7 +6682,7 @@
       <c r="J151" s="99"/>
       <c r="K151" s="15"/>
     </row>
-    <row r="152" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A152" s="18"/>
       <c r="B152" s="24"/>
       <c r="C152" s="18"/>
@@ -6695,7 +6695,7 @@
       <c r="J152" s="99"/>
       <c r="K152" s="15"/>
     </row>
-    <row r="153" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A153" s="18" t="s">
         <v>61</v>
       </c>
@@ -6710,7 +6710,7 @@
       <c r="J153" s="99"/>
       <c r="K153" s="15"/>
     </row>
-    <row r="154" spans="1:11" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A154" s="15">
         <v>1</v>
       </c>
@@ -6731,7 +6731,7 @@
       <c r="J154" s="99"/>
       <c r="K154" s="15"/>
     </row>
-    <row r="155" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A155" s="15">
         <v>2</v>
       </c>
@@ -6756,7 +6756,7 @@
       <c r="J155" s="99"/>
       <c r="K155" s="15"/>
     </row>
-    <row r="156" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A156" s="15">
         <v>3</v>
       </c>
@@ -6781,7 +6781,7 @@
       <c r="J156" s="99"/>
       <c r="K156" s="15"/>
     </row>
-    <row r="157" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A157" s="18" t="s">
         <v>63</v>
       </c>
@@ -6796,7 +6796,7 @@
       <c r="J157" s="99"/>
       <c r="K157" s="15"/>
     </row>
-    <row r="158" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A158" s="5">
         <v>1</v>
       </c>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="J158" s="97"/>
     </row>
-    <row r="159" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A159" s="5">
         <v>2</v>
       </c>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="J159" s="97"/>
     </row>
-    <row r="160" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="5">
         <v>3</v>
       </c>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="J160" s="97"/>
     </row>
-    <row r="161" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A161" s="5">
         <v>4</v>
       </c>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="J161" s="97"/>
     </row>
-    <row r="162" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A162" s="5">
         <v>5</v>
       </c>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="J162" s="97"/>
     </row>
-    <row r="163" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" ht="30" x14ac:dyDescent="0.2">
       <c r="A163" s="5">
         <v>6</v>
       </c>
@@ -6938,7 +6938,7 @@
       <c r="I163" s="20"/>
       <c r="J163" s="97"/>
     </row>
-    <row r="164" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A164" s="5">
         <v>7</v>
       </c>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="J164" s="97"/>
     </row>
-    <row r="165" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A165" s="5">
         <v>8</v>
       </c>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="J165" s="97"/>
     </row>
-    <row r="166" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A166" s="5">
         <v>9</v>
       </c>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="J166" s="97"/>
     </row>
-    <row r="167" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A167" s="5">
         <v>10</v>
       </c>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="J167" s="97"/>
     </row>
-    <row r="168" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A168" s="5">
         <v>11</v>
       </c>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="J168" s="97"/>
     </row>
-    <row r="169" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A169" s="5">
         <v>12</v>
       </c>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="J169" s="97"/>
     </row>
-    <row r="170" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A170" s="5">
         <v>13</v>
       </c>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="J170" s="97"/>
     </row>
-    <row r="171" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A171" s="5">
         <v>14</v>
       </c>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="J171" s="97"/>
     </row>
-    <row r="172" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A172" s="5">
         <v>15</v>
       </c>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="J172" s="97"/>
     </row>
-    <row r="173" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A173" s="5">
         <v>16</v>
       </c>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="J173" s="97"/>
     </row>
-    <row r="174" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A174" s="5">
         <v>17</v>
       </c>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="J174" s="97"/>
     </row>
-    <row r="175" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A175" s="5">
         <v>18</v>
       </c>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="J175" s="97"/>
     </row>
-    <row r="176" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A176" s="5">
         <v>19</v>
       </c>
@@ -7248,7 +7248,7 @@
       <c r="I176" s="20"/>
       <c r="J176" s="97"/>
     </row>
-    <row r="179" spans="1:11" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="103" t="s">
         <v>151</v>
       </c>
@@ -7264,7 +7264,7 @@
       <c r="I179" s="36"/>
       <c r="K179" s="101"/>
     </row>
-    <row r="182" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
@@ -7273,7 +7273,7 @@
       <c r="J182" s="1"/>
       <c r="K182" s="5"/>
     </row>
-    <row r="183" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
@@ -7282,7 +7282,7 @@
       <c r="J183" s="1"/>
       <c r="K183" s="5"/>
     </row>
-    <row r="184" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
@@ -7291,7 +7291,7 @@
       <c r="J184" s="1"/>
       <c r="K184" s="5"/>
     </row>
-    <row r="185" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
@@ -7300,7 +7300,7 @@
       <c r="J185" s="1"/>
       <c r="K185" s="5"/>
     </row>
-    <row r="186" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
@@ -7309,7 +7309,7 @@
       <c r="J186" s="1"/>
       <c r="K186" s="5"/>
     </row>
-    <row r="187" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
@@ -7318,7 +7318,7 @@
       <c r="J187" s="1"/>
       <c r="K187" s="5"/>
     </row>
-    <row r="188" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
@@ -7327,7 +7327,7 @@
       <c r="J188" s="1"/>
       <c r="K188" s="5"/>
     </row>
-    <row r="189" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
@@ -7336,7 +7336,7 @@
       <c r="J189" s="1"/>
       <c r="K189" s="5"/>
     </row>
-    <row r="190" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
@@ -7345,7 +7345,7 @@
       <c r="J190" s="1"/>
       <c r="K190" s="5"/>
     </row>
-    <row r="191" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
@@ -7354,7 +7354,7 @@
       <c r="J191" s="1"/>
       <c r="K191" s="5"/>
     </row>
-    <row r="192" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
@@ -7363,7 +7363,7 @@
       <c r="J192" s="1"/>
       <c r="K192" s="5"/>
     </row>
-    <row r="193" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
@@ -7372,7 +7372,7 @@
       <c r="J193" s="1"/>
       <c r="K193" s="5"/>
     </row>
-    <row r="194" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
@@ -7381,7 +7381,7 @@
       <c r="J194" s="1"/>
       <c r="K194" s="5"/>
     </row>
-    <row r="195" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
@@ -7390,7 +7390,7 @@
       <c r="J195" s="1"/>
       <c r="K195" s="5"/>
     </row>
-    <row r="196" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
@@ -7399,7 +7399,7 @@
       <c r="J196" s="1"/>
       <c r="K196" s="5"/>
     </row>
-    <row r="197" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
@@ -7408,7 +7408,7 @@
       <c r="J197" s="1"/>
       <c r="K197" s="5"/>
     </row>
-    <row r="198" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
@@ -7417,7 +7417,7 @@
       <c r="J198" s="1"/>
       <c r="K198" s="5"/>
     </row>
-    <row r="199" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
@@ -7426,7 +7426,7 @@
       <c r="J199" s="1"/>
       <c r="K199" s="5"/>
     </row>
-    <row r="200" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
@@ -7435,7 +7435,7 @@
       <c r="J200" s="1"/>
       <c r="K200" s="5"/>
     </row>
-    <row r="201" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
@@ -7444,7 +7444,7 @@
       <c r="J201" s="1"/>
       <c r="K201" s="5"/>
     </row>
-    <row r="202" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
@@ -7453,7 +7453,7 @@
       <c r="J202" s="1"/>
       <c r="K202" s="5"/>
     </row>
-    <row r="203" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
@@ -7462,7 +7462,7 @@
       <c r="J203" s="1"/>
       <c r="K203" s="5"/>
     </row>
-    <row r="204" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
@@ -7471,7 +7471,7 @@
       <c r="J204" s="1"/>
       <c r="K204" s="5"/>
     </row>
-    <row r="205" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
@@ -7480,7 +7480,7 @@
       <c r="J205" s="1"/>
       <c r="K205" s="5"/>
     </row>
-    <row r="206" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
@@ -7489,7 +7489,7 @@
       <c r="J206" s="1"/>
       <c r="K206" s="5"/>
     </row>
-    <row r="207" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
@@ -7498,7 +7498,7 @@
       <c r="J207" s="1"/>
       <c r="K207" s="5"/>
     </row>
-    <row r="208" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
@@ -7507,7 +7507,7 @@
       <c r="J208" s="1"/>
       <c r="K208" s="5"/>
     </row>
-    <row r="209" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
@@ -7516,7 +7516,7 @@
       <c r="J209" s="1"/>
       <c r="K209" s="5"/>
     </row>
-    <row r="210" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
@@ -7525,7 +7525,7 @@
       <c r="J210" s="1"/>
       <c r="K210" s="5"/>
     </row>
-    <row r="211" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
@@ -7534,7 +7534,7 @@
       <c r="J211" s="1"/>
       <c r="K211" s="5"/>
     </row>
-    <row r="212" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
@@ -7543,7 +7543,7 @@
       <c r="J212" s="1"/>
       <c r="K212" s="5"/>
     </row>
-    <row r="213" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
@@ -7552,7 +7552,7 @@
       <c r="J213" s="1"/>
       <c r="K213" s="5"/>
     </row>
-    <row r="214" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
@@ -7561,7 +7561,7 @@
       <c r="J214" s="1"/>
       <c r="K214" s="5"/>
     </row>
-    <row r="215" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
@@ -7570,7 +7570,7 @@
       <c r="J215" s="1"/>
       <c r="K215" s="5"/>
     </row>
-    <row r="216" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
@@ -7579,7 +7579,7 @@
       <c r="J216" s="1"/>
       <c r="K216" s="5"/>
     </row>
-    <row r="217" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
@@ -7588,7 +7588,7 @@
       <c r="J217" s="1"/>
       <c r="K217" s="5"/>
     </row>
-    <row r="218" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
@@ -7597,7 +7597,7 @@
       <c r="J218" s="1"/>
       <c r="K218" s="5"/>
     </row>
-    <row r="219" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
@@ -7606,7 +7606,7 @@
       <c r="J219" s="1"/>
       <c r="K219" s="5"/>
     </row>
-    <row r="220" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
@@ -7615,7 +7615,7 @@
       <c r="J220" s="1"/>
       <c r="K220" s="5"/>
     </row>
-    <row r="221" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
@@ -7624,7 +7624,7 @@
       <c r="J221" s="1"/>
       <c r="K221" s="5"/>
     </row>
-    <row r="222" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
@@ -7633,7 +7633,7 @@
       <c r="J222" s="1"/>
       <c r="K222" s="5"/>
     </row>
-    <row r="223" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
@@ -7642,7 +7642,7 @@
       <c r="J223" s="1"/>
       <c r="K223" s="5"/>
     </row>
-    <row r="224" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
@@ -7651,7 +7651,7 @@
       <c r="J224" s="1"/>
       <c r="K224" s="5"/>
     </row>
-    <row r="225" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
@@ -7660,7 +7660,7 @@
       <c r="J225" s="1"/>
       <c r="K225" s="5"/>
     </row>
-    <row r="226" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
@@ -7669,7 +7669,7 @@
       <c r="J226" s="1"/>
       <c r="K226" s="5"/>
     </row>
-    <row r="227" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
@@ -7678,7 +7678,7 @@
       <c r="J227" s="1"/>
       <c r="K227" s="5"/>
     </row>
-    <row r="228" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
@@ -7687,7 +7687,7 @@
       <c r="J228" s="1"/>
       <c r="K228" s="5"/>
     </row>
-    <row r="229" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
@@ -7696,7 +7696,7 @@
       <c r="J229" s="1"/>
       <c r="K229" s="5"/>
     </row>
-    <row r="230" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
@@ -7705,7 +7705,7 @@
       <c r="J230" s="1"/>
       <c r="K230" s="5"/>
     </row>
-    <row r="231" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
@@ -7714,7 +7714,7 @@
       <c r="J231" s="1"/>
       <c r="K231" s="5"/>
     </row>
-    <row r="232" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
@@ -7723,7 +7723,7 @@
       <c r="J232" s="1"/>
       <c r="K232" s="5"/>
     </row>
-    <row r="233" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
@@ -7732,7 +7732,7 @@
       <c r="J233" s="1"/>
       <c r="K233" s="5"/>
     </row>
-    <row r="234" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
@@ -7741,7 +7741,7 @@
       <c r="J234" s="1"/>
       <c r="K234" s="5"/>
     </row>
-    <row r="235" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
@@ -7750,7 +7750,7 @@
       <c r="J235" s="1"/>
       <c r="K235" s="5"/>
     </row>
-    <row r="236" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
@@ -7759,7 +7759,7 @@
       <c r="J236" s="1"/>
       <c r="K236" s="5"/>
     </row>
-    <row r="237" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
@@ -7768,7 +7768,7 @@
       <c r="J237" s="1"/>
       <c r="K237" s="5"/>
     </row>
-    <row r="238" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
@@ -7777,7 +7777,7 @@
       <c r="J238" s="1"/>
       <c r="K238" s="5"/>
     </row>
-    <row r="239" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
@@ -7786,7 +7786,7 @@
       <c r="J239" s="1"/>
       <c r="K239" s="5"/>
     </row>
-    <row r="240" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
@@ -7795,7 +7795,7 @@
       <c r="J240" s="1"/>
       <c r="K240" s="5"/>
     </row>
-    <row r="241" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
@@ -7804,7 +7804,7 @@
       <c r="J241" s="1"/>
       <c r="K241" s="5"/>
     </row>
-    <row r="242" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
@@ -7813,7 +7813,7 @@
       <c r="J242" s="1"/>
       <c r="K242" s="5"/>
     </row>
-    <row r="243" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
@@ -7822,7 +7822,7 @@
       <c r="J243" s="1"/>
       <c r="K243" s="5"/>
     </row>
-    <row r="244" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
@@ -7831,7 +7831,7 @@
       <c r="J244" s="1"/>
       <c r="K244" s="5"/>
     </row>
-    <row r="245" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
@@ -7840,7 +7840,7 @@
       <c r="J245" s="1"/>
       <c r="K245" s="5"/>
     </row>
-    <row r="246" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
@@ -7849,7 +7849,7 @@
       <c r="J246" s="1"/>
       <c r="K246" s="5"/>
     </row>
-    <row r="247" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
@@ -7858,7 +7858,7 @@
       <c r="J247" s="1"/>
       <c r="K247" s="5"/>
     </row>
-    <row r="248" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
@@ -7867,7 +7867,7 @@
       <c r="J248" s="1"/>
       <c r="K248" s="5"/>
     </row>
-    <row r="249" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
@@ -7876,7 +7876,7 @@
       <c r="J249" s="1"/>
       <c r="K249" s="5"/>
     </row>
-    <row r="250" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
@@ -7885,7 +7885,7 @@
       <c r="J250" s="1"/>
       <c r="K250" s="5"/>
     </row>
-    <row r="251" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
@@ -7894,7 +7894,7 @@
       <c r="J251" s="1"/>
       <c r="K251" s="5"/>
     </row>
-    <row r="252" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
@@ -7903,7 +7903,7 @@
       <c r="J252" s="1"/>
       <c r="K252" s="5"/>
     </row>
-    <row r="253" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
@@ -7912,7 +7912,7 @@
       <c r="J253" s="1"/>
       <c r="K253" s="5"/>
     </row>
-    <row r="254" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
@@ -7921,7 +7921,7 @@
       <c r="J254" s="1"/>
       <c r="K254" s="5"/>
     </row>
-    <row r="255" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
@@ -7930,7 +7930,7 @@
       <c r="J255" s="1"/>
       <c r="K255" s="5"/>
     </row>
-    <row r="256" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
@@ -7939,7 +7939,7 @@
       <c r="J256" s="1"/>
       <c r="K256" s="5"/>
     </row>
-    <row r="257" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
@@ -7948,7 +7948,7 @@
       <c r="J257" s="1"/>
       <c r="K257" s="5"/>
     </row>
-    <row r="258" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
@@ -7957,7 +7957,7 @@
       <c r="J258" s="1"/>
       <c r="K258" s="5"/>
     </row>
-    <row r="259" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="C259" s="1"/>
       <c r="D259" s="1"/>
@@ -7966,7 +7966,7 @@
       <c r="J259" s="1"/>
       <c r="K259" s="5"/>
     </row>
-    <row r="260" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="C260" s="1"/>
       <c r="D260" s="1"/>
@@ -8025,15 +8025,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3B58F3-4F81-4374-839A-DA060915BB5F}">
   <dimension ref="A1:C55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <col min="2" max="2" width="34.33203125" style="62" customWidth="1"/>
-    <col min="3" max="3" width="49.33203125" style="62" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" style="62" customWidth="1"/>
+    <col min="3" max="3" width="49.28515625" style="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:3" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:3" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>317</v>
       </c>
@@ -8044,7 +8044,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A3" s="57">
         <v>1</v>
       </c>
@@ -8055,7 +8055,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="57">
         <v>2</v>
       </c>
@@ -8066,7 +8066,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A5" s="57">
         <v>3</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="57">
         <v>4</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" s="57">
         <v>5</v>
       </c>
@@ -8099,7 +8099,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="57">
         <v>6</v>
       </c>
@@ -8110,7 +8110,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" s="57">
         <v>7</v>
       </c>
@@ -8121,7 +8121,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="57">
         <v>8</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="57">
         <v>9</v>
       </c>
@@ -8143,7 +8143,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A12" s="57">
         <v>10</v>
       </c>
@@ -8154,7 +8154,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="57">
         <v>11</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="69" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A14" s="57">
         <v>12</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="57">
         <v>13</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A16" s="57">
         <v>14</v>
       </c>
@@ -8198,7 +8198,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="69" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A17" s="57">
         <v>15</v>
       </c>
@@ -8209,7 +8209,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A18" s="57">
         <v>16</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A19" s="57">
         <v>17</v>
       </c>
@@ -8231,7 +8231,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="57">
         <v>18</v>
       </c>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="C20" s="60"/>
     </row>
-    <row r="21" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A21" s="57">
         <v>19</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="57">
         <v>20</v>
       </c>
@@ -8262,7 +8262,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A23" s="57">
         <v>21</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A24" s="57">
         <v>22</v>
       </c>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C24" s="60"/>
     </row>
-    <row r="25" spans="1:3" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A25" s="58">
         <v>23</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" s="57">
         <v>24</v>
       </c>
@@ -8304,7 +8304,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A27" s="57">
         <v>25</v>
       </c>
@@ -8315,7 +8315,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A28" s="57">
         <v>26</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="57">
         <v>27</v>
       </c>
@@ -8337,7 +8337,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="57">
         <v>28</v>
       </c>
@@ -8348,7 +8348,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="57">
         <v>29</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A32" s="57">
         <v>30</v>
       </c>
@@ -8370,7 +8370,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="57">
         <v>31</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A34" s="57">
         <v>32</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A35" s="57">
         <v>33</v>
       </c>
@@ -8403,7 +8403,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A36" s="57">
         <v>34</v>
       </c>
@@ -8414,7 +8414,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="57">
         <v>35</v>
       </c>
@@ -8425,7 +8425,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A38" s="57">
         <v>36</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="57">
         <v>37</v>
       </c>
@@ -8447,7 +8447,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" s="57">
         <v>38</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A41" s="57">
         <v>39</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="69" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A42" s="57">
         <v>40</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" s="57">
         <v>41</v>
       </c>
@@ -8491,7 +8491,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A44" s="57">
         <v>42</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="57">
         <v>43</v>
       </c>
@@ -8513,7 +8513,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A46" s="57">
         <v>44</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A47" s="57">
         <v>45</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="57">
         <v>46</v>
       </c>
@@ -8546,7 +8546,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A49" s="57">
         <v>47</v>
       </c>
@@ -8557,7 +8557,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A50" s="57">
         <v>48</v>
       </c>
@@ -8568,7 +8568,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="57">
         <v>49</v>
       </c>
@@ -8579,7 +8579,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A52" s="57">
         <v>50</v>
       </c>
@@ -8590,7 +8590,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="57">
         <v>51</v>
       </c>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="C53" s="66"/>
     </row>
-    <row r="54" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A54" s="57">
         <v>51</v>
       </c>
@@ -8610,7 +8610,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A55" s="57">
         <v>52</v>
       </c>

--- a/Biosci Reader_06.04.26.xlsx
+++ b/Biosci Reader_06.04.26.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E35092-E79F-486A-AA3C-50FE94C83D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E1C1EB-DA1F-48F8-B47C-9C8625C40109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="218" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,15 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -4109,7 +4100,9 @@
       <c r="J47" s="99" t="s">
         <v>550</v>
       </c>
-      <c r="K47" s="12"/>
+      <c r="K47" s="12">
+        <v>5</v>
+      </c>
     </row>
     <row r="48" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="18"/>
@@ -4265,7 +4258,9 @@
       <c r="J53" s="99" t="s">
         <v>551</v>
       </c>
-      <c r="K53" s="12"/>
+      <c r="K53" s="12">
+        <v>5</v>
+      </c>
     </row>
     <row r="54" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="18"/>
@@ -4952,7 +4947,9 @@
       <c r="J78" s="99" t="s">
         <v>550</v>
       </c>
-      <c r="K78" s="15"/>
+      <c r="K78" s="15">
+        <v>5</v>
+      </c>
     </row>
     <row r="79" spans="1:11" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="15"/>
@@ -5421,7 +5418,9 @@
         <v>20</v>
       </c>
       <c r="J95" s="99"/>
-      <c r="K95" s="15"/>
+      <c r="K95" s="15">
+        <v>5</v>
+      </c>
     </row>
     <row r="96" spans="1:11" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="18"/>

--- a/Biosci Reader_06.04.26.xlsx
+++ b/Biosci Reader_06.04.26.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E1C1EB-DA1F-48F8-B47C-9C8625C40109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060FA4CC-500F-4969-8EAD-90A9033EBFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="218" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2969,9 +2969,9 @@
     <col min="5" max="5" width="45.42578125" style="3" customWidth="1"/>
     <col min="6" max="6" width="8.28515625" style="2" customWidth="1"/>
     <col min="7" max="7" width="8.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20" style="2" customWidth="1"/>
-    <col min="9" max="9" width="42.7109375" style="34" customWidth="1"/>
-    <col min="10" max="10" width="37.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39.42578125" style="34" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.28515625" style="5"/>
     <col min="12" max="16384" width="9.28515625" style="1"/>
   </cols>
